--- a/dados/excel/secretaria_gini.xlsx
+++ b/dados/excel/secretaria_gini.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -753,10 +753,10 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C2" s="10" t="n">
-        <v>0.301</v>
+        <v>0.2976</v>
       </c>
     </row>
     <row r="3">
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>0.2884</v>
+        <v>0.296</v>
       </c>
     </row>
     <row r="4">
@@ -779,10 +779,10 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>8116</v>
+        <v>8653</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>0.4675</v>
+        <v>0.445</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         <v>164</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>0.3737</v>
+        <v>0.3076</v>
       </c>
     </row>
     <row r="6">
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>2865</v>
+        <v>2861</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.3747</v>
+        <v>0.3701</v>
       </c>
     </row>
     <row r="7">
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.3987</v>
+        <v>0.4036</v>
       </c>
     </row>
     <row r="8">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>0.5288</v>
+        <v>0.5069</v>
       </c>
     </row>
     <row r="9">
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>0.4935</v>
+        <v>0.4485</v>
       </c>
     </row>
     <row r="10">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>0.3672</v>
+        <v>0.3632</v>
       </c>
     </row>
     <row r="11">
@@ -870,10 +870,10 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.432</v>
+        <v>0.4772</v>
       </c>
     </row>
     <row r="12">
@@ -883,10 +883,10 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>0.404</v>
+        <v>0.4075</v>
       </c>
     </row>
     <row r="13">
@@ -899,7 +899,7 @@
         <v>73</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>0.3865</v>
+        <v>0.4072</v>
       </c>
     </row>
     <row r="14">
@@ -912,7 +912,7 @@
         <v>55</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>0.3466</v>
+        <v>0.3729</v>
       </c>
     </row>
     <row r="15">
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>0.3699</v>
+        <v>0.3777</v>
       </c>
     </row>
     <row r="16">
@@ -938,7 +938,7 @@
         <v>129</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>0.3737</v>
+        <v>0.3544</v>
       </c>
     </row>
     <row r="17">
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>0.2896</v>
+        <v>0.2978</v>
       </c>
     </row>
     <row r="18">
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>0.3232</v>
+        <v>0.3327</v>
       </c>
     </row>
     <row r="19">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>0.3858</v>
+        <v>0.3663</v>
       </c>
     </row>
   </sheetData>
